--- a/data/trans_dic/IP1008-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1008-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen trastornos huesos, articulaciones o musculares</t>
+          <t>Menores que padecen trastornos huesos, articulaciones o musculares (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 2,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,88</t>
+          <t>0,0; 3,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,35</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,73</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 1,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,48</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,21</t>
+          <t>0,0; 2,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,27</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,18</t>
+          <t>0,13; 1,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,91</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,1</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,83</t>
+          <t>0,0; 3,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,29</t>
+          <t>0,33; 3,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,39</t>
+          <t>0,0; 2,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,83</t>
+          <t>0,19; 1,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,56</t>
+          <t>0,0; 1,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,72</t>
+          <t>0,16; 1,82</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,84</t>
+          <t>0,34; 2,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,66</t>
+          <t>0,36; 3,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,65</t>
+          <t>0,0; 1,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,31</t>
+          <t>0,36; 3,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,96</t>
+          <t>0,34; 3,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,57</t>
+          <t>0,17; 1,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,81</t>
+          <t>0,19; 1,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,65</t>
+          <t>0,58; 2,63</t>
         </is>
       </c>
     </row>
@@ -1117,37 +1118,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,14</t>
+          <t>0,17; 1,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,22</t>
+          <t>0,19; 1,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,67</t>
+          <t>0,4; 1,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,23</t>
+          <t>0,28; 1,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,97</t>
+          <t>0,17; 0,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,77</t>
+          <t>0,08; 0,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,92</t>
+          <t>0,27; 0,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1157,7 +1158,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,94</t>
+          <t>0,32; 0,96</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen trastornos huesos, articulaciones o musculares (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3766</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3946</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3409</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3611</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4827</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1375</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1358</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1375</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3249</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5411</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4827</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4598</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>640; 5419</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5003</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4180</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1390</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2313</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1358</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1885</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1390</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2313</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3063</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4881</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>616; 6804</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4107</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>522; 5118</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5017</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>617; 6874</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2052</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2547</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2593</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2731</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2593</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>4496</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>652; 5378</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>626; 6477</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3413</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>647; 6230</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>585; 5359</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>678; 6712</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>650; 5910</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2025; 9125</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3220</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3498</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6235</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>3267</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>7321</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>6765</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>8183</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1184; 7671</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1355; 7909</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2847; 11565</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2018; 9021</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1281; 7323</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>584; 5077</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3760; 12663</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>3337; 12194</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>4688; 13915</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1008-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1008-Edad-trans_dic.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,57</t>
+          <t>0,0; 2,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,25</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,36</t>
+          <t>0,0; 2,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 1,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,66</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -788,22 +788,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,31</t>
+          <t>0,0; 2,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,81</t>
+          <t>0,0; 1,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -818,17 +818,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,07</t>
+          <t>0,13; 1,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,0</t>
+          <t>0,0; 1,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,0; 1,17</t>
         </is>
       </c>
     </row>
@@ -898,22 +898,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,0; 2,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,15</t>
+          <t>0,0; 3,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,6</t>
+          <t>0,32; 3,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,9</t>
+          <t>0,0; 3,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,9</t>
+          <t>0,19; 1,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,6</t>
+          <t>0,0; 1,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,82</t>
+          <t>0,16; 1,68</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,77</t>
+          <t>0,34; 3,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,74</t>
+          <t>0,37; 3,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,5</t>
+          <t>0,37; 3,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,69</t>
+          <t>0,2; 1,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,63</t>
+          <t>0,55; 2,53</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,13</t>
+          <t>0,17; 1,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,12</t>
+          <t>0,19; 1,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,64</t>
+          <t>0,4; 1,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,25</t>
+          <t>0,19; 1,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,98</t>
+          <t>0,17; 0,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,68</t>
+          <t>0,08; 0,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,9</t>
+          <t>0,28; 0,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,84</t>
+          <t>0,23; 0,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,96</t>
+          <t>0,29; 0,95</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3766</t>
+          <t>0; 3811</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3946</t>
+          <t>0; 3331</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3409</t>
+          <t>0; 3389</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3611</t>
+          <t>0; 4036</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4827</t>
+          <t>0; 4386</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1580,22 +1580,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3249</t>
+          <t>0; 3850</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5411</t>
+          <t>0; 5115</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4827</t>
+          <t>0; 4206</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4598</t>
+          <t>0; 4105</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>640; 5419</t>
+          <t>640; 5663</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5003</t>
+          <t>0; 5355</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4180</t>
+          <t>0; 5477</t>
         </is>
       </c>
     </row>
@@ -1743,22 +1743,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3063</t>
+          <t>0; 3236</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4881</t>
+          <t>0; 4706</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>616; 6804</t>
+          <t>612; 6213</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4107</t>
+          <t>0; 4752</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1773,17 +1773,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>522; 5118</t>
+          <t>524; 5181</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 5017</t>
+          <t>0; 4794</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>617; 6874</t>
+          <t>617; 6330</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>652; 5378</t>
+          <t>653; 6133</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1916,37 +1916,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>626; 6477</t>
+          <t>647; 5852</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3413</t>
+          <t>0; 3419</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>647; 6230</t>
+          <t>653; 6351</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>585; 5359</t>
+          <t>585; 5368</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>678; 6712</t>
+          <t>684; 6726</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>650; 5910</t>
+          <t>685; 6464</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2025; 9125</t>
+          <t>1908; 8776</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1184; 7671</t>
+          <t>1183; 7365</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1355; 7909</t>
+          <t>1358; 8233</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2847; 11565</t>
+          <t>2826; 11751</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2018; 9021</t>
+          <t>1378; 8198</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1281; 7323</t>
+          <t>1256; 7159</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>584; 5077</t>
+          <t>587; 5421</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3760; 12663</t>
+          <t>3992; 12893</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3337; 12194</t>
+          <t>3368; 11708</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4688; 13915</t>
+          <t>4209; 13786</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1008-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1008-Edad-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,27 +625,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,43%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -678,27 +678,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,88</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,35</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,61</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,74</t>
-        </is>
-      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,34</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>0,0; 1,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,51</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,65%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,62</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,12</t>
+          <t>0,13; 1,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,07</t>
+          <t>0,0; 0,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,17</t>
+          <t>0,0; 1,1</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,9%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,22%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,54</t>
+          <t>0,0; 3,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,07</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,83</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>0,32; 3,29</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,36</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,93</t>
+          <t>0,2; 1,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,53</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,68</t>
+          <t>0,16; 1,72</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>1,06%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1,47%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,16</t>
+          <t>0,0; 1,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>0,37; 3,31</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0,33; 2,96</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0,33; 2,84</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,37; 3,38</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,66</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,37; 3,57</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,08</t>
+          <t>0,36; 3,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,68</t>
+          <t>0,17; 1,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,85</t>
+          <t>0,19; 1,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,53</t>
+          <t>0,56; 2,65</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,47%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,49%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0,89%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,32 +1118,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,08</t>
+          <t>0,19; 1,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,16</t>
+          <t>0,17; 0,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,67</t>
+          <t>0,08; 0,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,13</t>
+          <t>0,17; 1,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,96</t>
+          <t>0,19; 1,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,73</t>
+          <t>0,41; 1,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,8</t>
+          <t>0,23; 0,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,95</t>
+          <t>0,29; 0,94</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,22 +1311,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1364,27 +1364,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>627</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>674</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1417,27 +1417,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0; 3500</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3399</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3811</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3331</t>
-        </is>
-      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3389</t>
+          <t>0; 2808</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4036</t>
+          <t>0; 3939</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4386</t>
+          <t>0; 4577</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1358</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1480</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1375</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1358</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3850</t>
+          <t>0; 4098</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5115</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4206</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4105</t>
+          <t>0; 3000</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 5183</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4789</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>640; 5663</t>
+          <t>641; 5982</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5355</t>
+          <t>0; 4565</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 5477</t>
+          <t>0; 5145</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1358</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>527</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>1390</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2313</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1358</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3236</t>
+          <t>0; 4802</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4706</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>612; 6213</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4752</t>
+          <t>0; 2642</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4382</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>609; 6215</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>524; 5181</t>
+          <t>527; 4929</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4794</t>
+          <t>0; 4894</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>617; 6330</t>
+          <t>617; 6509</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2593</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>2052</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2547</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2593</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1949</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>653; 6133</t>
+          <t>0; 3397</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>650; 5888</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>580; 5157</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>650; 5508</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>647; 5852</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>0; 3419</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>653; 6351</t>
-        </is>
-      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>585; 5368</t>
+          <t>627; 6345</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>684; 6726</t>
+          <t>679; 6266</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>685; 6464</t>
+          <t>651; 6338</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1908; 8776</t>
+          <t>1945; 9220</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3267</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>3220</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>3498</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>6235</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>4101</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>3267</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1949</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1183; 7365</t>
+          <t>1381; 8886</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1358; 8233</t>
+          <t>1282; 7240</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2826; 11751</t>
+          <t>588; 5708</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1378; 8198</t>
+          <t>1167; 7780</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1256; 7159</t>
+          <t>1360; 8640</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>587; 5421</t>
+          <t>2906; 11767</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3992; 12893</t>
+          <t>3899; 12960</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3368; 11708</t>
+          <t>3401; 12177</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4209; 13786</t>
+          <t>4177; 13601</t>
         </is>
       </c>
     </row>
